--- a/kaggle_results/T11-23-2025/coreference_resolution_cache.xlsx
+++ b/kaggle_results/T11-23-2025/coreference_resolution_cache.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.git_projs\MedicalQA\kaggle_results\T11-23-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9ED81E2-A2F7-486D-A486-BC6E78830917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2203701-BC41-4803-A27A-E375130EA12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11815,7 +11815,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11825,6 +11825,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11856,13 +11862,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12169,6 +12178,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F942"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="4" width="85.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -16284,17 +16296,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="70" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>582</v>
       </c>
       <c r="B243" t="s">
         <v>698</v>
       </c>
-      <c r="C243" t="s">
+      <c r="C243" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D243" t="s">
+      <c r="D243" s="4" t="s">
         <v>700</v>
       </c>
       <c r="E243">
@@ -27708,7 +27720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="915" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:6" s="2" customFormat="1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A915" s="2">
         <v>1607</v>
       </c>
